--- a/artfynd/A 20690-2024 artfynd.xlsx
+++ b/artfynd/A 20690-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136582887</v>
       </c>
       <c r="B2" t="n">
-        <v>101525</v>
+        <v>101528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20690-2024 artfynd.xlsx
+++ b/artfynd/A 20690-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136582887</v>
       </c>
       <c r="B2" t="n">
-        <v>101528</v>
+        <v>101529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20690-2024 artfynd.xlsx
+++ b/artfynd/A 20690-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136582887</v>
       </c>
       <c r="B2" t="n">
-        <v>101529</v>
+        <v>101534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20690-2024 artfynd.xlsx
+++ b/artfynd/A 20690-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136582887</v>
       </c>
       <c r="B2" t="n">
-        <v>101534</v>
+        <v>101536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20690-2024 artfynd.xlsx
+++ b/artfynd/A 20690-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136582887</v>
       </c>
       <c r="B2" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20690-2024 artfynd.xlsx
+++ b/artfynd/A 20690-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136582887</v>
       </c>
       <c r="B2" t="n">
-        <v>101542</v>
+        <v>101544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20690-2024 artfynd.xlsx
+++ b/artfynd/A 20690-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136582887</v>
       </c>
       <c r="B2" t="n">
-        <v>101544</v>
+        <v>101545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20690-2024 artfynd.xlsx
+++ b/artfynd/A 20690-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136582887</v>
       </c>
       <c r="B2" t="n">
-        <v>101545</v>
+        <v>101551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20690-2024 artfynd.xlsx
+++ b/artfynd/A 20690-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136582887</v>
       </c>
       <c r="B2" t="n">
-        <v>101551</v>
+        <v>101555</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20690-2024 artfynd.xlsx
+++ b/artfynd/A 20690-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136582887</v>
       </c>
       <c r="B2" t="n">
-        <v>101555</v>
+        <v>101557</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20690-2024 artfynd.xlsx
+++ b/artfynd/A 20690-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136582887</v>
       </c>
       <c r="B2" t="n">
-        <v>101557</v>
+        <v>101559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
